--- a/business-libraries/test-data/learning_problem/attribution.xlsx
+++ b/business-libraries/test-data/learning_problem/attribution.xlsx
@@ -4,8 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="⑤b 归因-计算变量" sheetId="1" r:id="rId1"/>
-    <sheet name="⑤c 归因-分级规则" sheetId="2" r:id="rId2"/>
-    <sheet name="⑥ 归因-红线熔断" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤c 归因项" sheetId="2" r:id="rId2"/>
+    <sheet name="⑤d 证据规则" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤e 分级规则" sheetId="4" r:id="rId4"/>
+    <sheet name="⑥ 归因-红线熔断" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,7 +428,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>总负荷指数</v>
+        <v>诊断总分</v>
       </c>
       <c r="B2" t="str">
         <v>learning_problem</v>
@@ -435,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>五题得分总和</v>
+        <v>三层诊断总分</v>
       </c>
       <c r="E2" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -447,367 +449,738 @@
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>情绪耗竭指数</v>
-      </c>
-      <c r="B3" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C3" t="str">
-        <v>维度[EMOTION]</v>
-      </c>
-      <c r="D3" t="str">
-        <v>情绪状态维度均值</v>
-      </c>
-      <c r="E3" t="str">
-        <v>LP_FIVE_Q</v>
-      </c>
-      <c r="F3" t="str">
-        <v>q1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>EMOTION</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>连续低意义感次数</v>
-      </c>
-      <c r="B4" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C4" t="str">
-        <v>COUNT_CONSECUTIVE(题[q3] &lt;= 2, 4)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>统计最近连续4次评估中意义感知得分&lt;=2的次数</v>
-      </c>
-      <c r="E4" t="str">
-        <v>LP_FIVE_Q</v>
-      </c>
-      <c r="F4" t="str">
-        <v>q3</v>
-      </c>
-      <c r="G4" t="str">
-        <v>MEANING</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>规则编码*</v>
+        <v>归因编码*</v>
       </c>
       <c r="B1" t="str">
+        <v>归因名称*</v>
+      </c>
+      <c r="C1" t="str">
         <v>所属模块*</v>
       </c>
-      <c r="C1" t="str">
-        <v>依据量表编码*</v>
-      </c>
       <c r="D1" t="str">
-        <v>优先级*</v>
+        <v>权重基数*</v>
       </c>
       <c r="E1" t="str">
-        <v>触发条件</v>
+        <v>工具标签*</v>
       </c>
       <c r="F1" t="str">
-        <v>命中等级*</v>
+        <v>归因说明</v>
       </c>
       <c r="G1" t="str">
-        <v>等级中文名*</v>
+        <v>高分表现</v>
       </c>
       <c r="H1" t="str">
-        <v>是否红线熔断*</v>
+        <v>典型诱因</v>
       </c>
       <c r="I1" t="str">
-        <v>主归因*</v>
+        <v>建议动作</v>
       </c>
       <c r="J1" t="str">
-        <v>次归因</v>
-      </c>
-      <c r="K1" t="str">
-        <v>归因理由*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>工具标签*</v>
-      </c>
-      <c r="M1" t="str">
-        <v>结果说明*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>输出动作摘要</v>
-      </c>
-      <c r="O1" t="str">
-        <v>输出工具摘要</v>
-      </c>
-      <c r="P1" t="str">
-        <v>升级条件</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>升级目标</v>
-      </c>
-      <c r="R1" t="str">
-        <v>复评触发条件</v>
-      </c>
-      <c r="S1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP-RED-Q1-Q3</v>
+        <v>LP_AT_BEHAVIOR</v>
       </c>
       <c r="B2" t="str">
+        <v>学习行为失序</v>
+      </c>
+      <c r="C2" t="str">
         <v>learning_problem</v>
       </c>
-      <c r="C2" t="str">
-        <v>LP_FIVE_Q</v>
-      </c>
       <c r="D2" t="str">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>learning_problem,behavior</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>学习行为持续失序，且提醒或奖励等外部推动手段效果有限。</v>
       </c>
       <c r="G2" t="str">
-        <v>需立即关注</v>
+        <v>作业拖延、课堂分心；提醒和奖励都不再有效</v>
       </c>
       <c r="H2" t="str">
-        <v>是</v>
+        <v>可能与执行功能、任务难度或环境干扰相关</v>
       </c>
       <c r="I2" t="str">
-        <v>注意力与策略双重薄弱</v>
+        <v>完成一周学习行为观察，记录课堂参与、作业完成和测验表现的模式</v>
       </c>
       <c r="J2" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Q1疲劳&gt;=4分且Q3意义感&lt;=2分，两者同时处于高危水平，教师可能正经历情绪耗竭的核心阶段</v>
-      </c>
-      <c r="L2" t="str">
-        <v>learning_problem,orange,focus</v>
-      </c>
-      <c r="M2" t="str">
-        <v>注意力与策略双重薄弱风险同时处于高位，已暂停常规建议并转介。</v>
-      </c>
-      <c r="N2" t="str">
-        <v>建议安排心理专员面谈，暂缓常规班级评估</v>
-      </c>
-      <c r="O2" t="str">
-        <v>番茄工作法指导（应急）、情绪温度计自评</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>下次评估Q1或Q3任一&gt;=3分时触发复评</v>
-      </c>
-      <c r="S2" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生学习问题手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP-ORANGE</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="B3" t="str">
+        <v>认知加工困难</v>
+      </c>
+      <c r="C3" t="str">
         <v>learning_problem</v>
       </c>
-      <c r="C3" t="str">
-        <v>LP_FIVE_Q</v>
-      </c>
       <c r="D3" t="str">
-        <v>20</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 17</v>
+        <v>learning_problem,cognition</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>学生对核心概念的理解停留在表面，缺少可迁移的学习策略。</v>
       </c>
       <c r="G3" t="str">
-        <v>需关注</v>
+        <v>会做原题不会变式；独立解题时容易卡住</v>
       </c>
       <c r="H3" t="str">
-        <v>否</v>
+        <v>缺少元认知策略或前置知识存在断层</v>
       </c>
       <c r="I3" t="str">
-        <v>作业完成度持续走低</v>
+        <v>试用一项教学支架：从示范、提示、提问、同伴互助中选一项并记录效果</v>
       </c>
       <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>总分&gt;=17分，教师在多个维度上感受到压力，但未达到红线阈值</v>
-      </c>
-      <c r="L3" t="str">
-        <v>learning_problem,yellow,analysis</v>
-      </c>
-      <c r="M3" t="str">
-        <v>您的整体状态在多个维度上偏高，建议重点关注并选择1-2项工具开始调整。</v>
-      </c>
-      <c r="N3" t="str">
-        <v>建议本月内完成一次深度自评</v>
-      </c>
-      <c r="O3" t="str">
-        <v>错题分析模板、学习策略训练</v>
-      </c>
-      <c r="P3" t="str">
-        <v>连续3次评估仍为orange</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>升级至red评估流程</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生学习问题手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP-YELLOW</v>
+        <v>LP_AT_RELATION</v>
       </c>
       <c r="B4" t="str">
+        <v>关系层影响</v>
+      </c>
+      <c r="C4" t="str">
         <v>learning_problem</v>
       </c>
-      <c r="C4" t="str">
-        <v>LP_FIVE_Q</v>
-      </c>
       <c r="D4" t="str">
-        <v>30</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="str">
-        <v>维度[EMOTION] &gt;= 3.5</v>
+        <v>learning_problem,relation</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>师生关系、同伴比较或家庭期待明显影响了学生的学习投入。</v>
       </c>
       <c r="G4" t="str">
-        <v>需留意</v>
+        <v>换老师后表现差异明显；因同伴比较而回避课堂</v>
       </c>
       <c r="H4" t="str">
-        <v>否</v>
+        <v>课堂归属感不足或家庭期待与能力错配</v>
       </c>
       <c r="I4" t="str">
-        <v>课堂参与严重不足</v>
+        <v>本周创造一次该学生在课堂上被正向看见的机会</v>
       </c>
       <c r="J4" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K4" t="str">
-        <v>情绪耗竭维度得分偏高，可能出现轻度职业倦怠的早期信号</v>
-      </c>
-      <c r="L4" t="str">
-        <v>learning_problem,orange,strategy</v>
-      </c>
-      <c r="M4" t="str">
-        <v>您的情绪耗竭维度偏高，建议开始关注自我照顾。</v>
-      </c>
-      <c r="N4" t="str">
-        <v>建议使用自我照顾工具</v>
-      </c>
-      <c r="O4" t="str">
-        <v>错题分析模板、同伴支持圈</v>
-      </c>
-      <c r="P4" t="str">
-        <v>连续2次评估仍为yellow</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>升级至orange评估流程</v>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生学习问题手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP-GREEN</v>
+        <v>LP_AT_MOTIVATION</v>
       </c>
       <c r="B5" t="str">
+        <v>内驱动机不足</v>
+      </c>
+      <c r="C5" t="str">
         <v>learning_problem</v>
       </c>
-      <c r="C5" t="str">
-        <v>LP_FIVE_Q</v>
-      </c>
       <c r="D5" t="str">
-        <v>100</v>
+        <v>1.1</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>learning_problem,motivation</v>
       </c>
       <c r="F5" t="str">
-        <v>green</v>
+        <v>学习完全依赖外部推动，学生缺少自主的学习目标。</v>
       </c>
       <c r="G5" t="str">
-        <v>状态良好</v>
+        <v>没人督促就不学；学习是为了避免批评</v>
       </c>
       <c r="H5" t="str">
-        <v>否</v>
+        <v>长期外部控制导致自主感缺失</v>
       </c>
       <c r="I5" t="str">
-        <v>状态稳定</v>
+        <v>让学生自己选择一项本周的学习任务并定义完成标准</v>
       </c>
       <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>当前评估未触发任何风险规则，教师整体状态稳定</v>
-      </c>
-      <c r="L5" t="str">
-        <v>learning_problem,green</v>
-      </c>
-      <c r="M5" t="str">
-        <v>当前状态整体稳定，保持现有节奏即可。</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LP_AT_EFFICACY</v>
+      </c>
+      <c r="B6" t="str">
+        <v>习得性无助</v>
+      </c>
+      <c r="C6" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1.4</v>
+      </c>
+      <c r="E6" t="str">
+        <v>learning_problem,efficacy</v>
+      </c>
+      <c r="F6" t="str">
+        <v>学生认为再努力也学不好，把失败归因于能力而非方法。</v>
+      </c>
+      <c r="G6" t="str">
+        <v>「我就是学不会数学」；放弃尝试</v>
+      </c>
+      <c r="H6" t="str">
+        <v>长期失败经验累积且缺少归因引导</v>
+      </c>
+      <c r="I6" t="str">
+        <v>设计一个必然能成功的最小任务，并明确把成功归因到具体方法上</v>
+      </c>
+      <c r="J6" t="str">
+        <v>学生学习问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>证据编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>归因编码*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>触发条件*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>证据权重*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>证据说明*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>LP_EV_01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>LP_AT_BEHAVIOR</v>
+      </c>
+      <c r="C2" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D2" t="str">
+        <v>维度[LP_BEHAVIOR] &gt;= 4</v>
+      </c>
+      <c r="E2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F2" t="str">
+        <v>行为层得分处于高位，学习行为持续失序</v>
+      </c>
+      <c r="G2" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>LP_EV_02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>LP_AT_BEHAVIOR</v>
+      </c>
+      <c r="C3" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D3" t="str">
+        <v>维度[LP_BEHAVIOR] &gt;= 3</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>行为层出现需要关注的信号</v>
+      </c>
+      <c r="G3" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>LP_EV_03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>LP_AT_BEHAVIOR</v>
+      </c>
+      <c r="C4" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D4" t="str">
+        <v>题[beh4] &gt;= 4</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2</v>
+      </c>
+      <c r="F4" t="str">
+        <v>提醒和奖励等外部推动手段已经失效</v>
+      </c>
+      <c r="G4" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>LP_EV_04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>LP_AT_COGNITION</v>
+      </c>
+      <c r="C5" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D5" t="str">
+        <v>维度[LP_COGNITION] &gt;= 4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>3</v>
+      </c>
+      <c r="F5" t="str">
+        <v>认知层得分处于高位，理解停留在表面</v>
+      </c>
+      <c r="G5" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LP_EV_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>LP_AT_COGNITION</v>
+      </c>
+      <c r="C6" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D6" t="str">
+        <v>维度[LP_COGNITION] &gt;= 3</v>
+      </c>
+      <c r="E6" t="str">
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>认知层出现需要关注的信号</v>
+      </c>
+      <c r="G6" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LP_EV_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>LP_AT_COGNITION</v>
+      </c>
+      <c r="C7" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D7" t="str">
+        <v>题[cog3] &gt;= 4</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2</v>
+      </c>
+      <c r="F7" t="str">
+        <v>缺少元认知策略，独立解题时容易卡住</v>
+      </c>
+      <c r="G7" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LP_EV_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>LP_AT_RELATION</v>
+      </c>
+      <c r="C8" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D8" t="str">
+        <v>维度[LP_RELATION] &gt;= 4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>3</v>
+      </c>
+      <c r="F8" t="str">
+        <v>关系层得分处于高位，关系因素明显影响学习</v>
+      </c>
+      <c r="G8" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LP_EV_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>LP_AT_RELATION</v>
+      </c>
+      <c r="C9" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D9" t="str">
+        <v>维度[LP_RELATION] &gt;= 3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>关系层出现需要关注的信号</v>
+      </c>
+      <c r="G9" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LP_EV_21</v>
+      </c>
+      <c r="B10" t="str">
+        <v>LP_AT_MOTIVATION</v>
+      </c>
+      <c r="C10" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="D10" t="str">
+        <v>维度[LP_INTRINSIC] &gt;= 3.5</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>内在动机维度偏低，学习依赖外部推动</v>
+      </c>
+      <c r="G10" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LP_EV_22</v>
+      </c>
+      <c r="B11" t="str">
+        <v>LP_AT_MOTIVATION</v>
+      </c>
+      <c r="C11" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="D11" t="str">
+        <v>维度[LP_INTRINSIC] &gt;= 3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>内在动机出现下降信号</v>
+      </c>
+      <c r="G11" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_EV_23</v>
+      </c>
+      <c r="B12" t="str">
+        <v>LP_AT_EFFICACY</v>
+      </c>
+      <c r="C12" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="D12" t="str">
+        <v>维度[LP_SELF_EFFICACY] &gt;= 3.5</v>
+      </c>
+      <c r="E12" t="str">
+        <v>3</v>
+      </c>
+      <c r="F12" t="str">
+        <v>学业自我效能偏低，出现习得性无助信号</v>
+      </c>
+      <c r="G12" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_EV_24</v>
+      </c>
+      <c r="B13" t="str">
+        <v>LP_AT_EFFICACY</v>
+      </c>
+      <c r="C13" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="D13" t="str">
+        <v>维度[LP_SELF_EFFICACY] &gt;= 3</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>学业自我效能需要关注</v>
+      </c>
+      <c r="G13" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_EV_25</v>
+      </c>
+      <c r="B14" t="str">
+        <v>LP_AT_RELATION</v>
+      </c>
+      <c r="C14" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="D14" t="str">
+        <v>维度[LP_ANXIETY] &gt;= 3.5</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2</v>
+      </c>
+      <c r="F14" t="str">
+        <v>学业焦虑明显，可能与课堂关系或家庭期待相关</v>
+      </c>
+      <c r="G14" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>规则编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>所属模块*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码</v>
+      </c>
+      <c r="D1" t="str">
+        <v>优先级*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="F1" t="str">
+        <v>命中等级*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>等级中文名*</v>
+      </c>
+      <c r="H1" t="str">
+        <v>严重度*</v>
+      </c>
+      <c r="I1" t="str">
+        <v>是否红线熔断*</v>
+      </c>
+      <c r="J1" t="str">
+        <v>结果说明*</v>
+      </c>
+      <c r="K1" t="str">
+        <v>升级条件</v>
+      </c>
+      <c r="L1" t="str">
+        <v>升级目标</v>
+      </c>
+      <c r="M1" t="str">
+        <v>复评触发条件</v>
+      </c>
+      <c r="N1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>LP_GRADE_LP3</v>
+      </c>
+      <c r="B2" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C2" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D2" t="str">
+        <v>10</v>
+      </c>
+      <c r="E2" t="str">
+        <v>诊断总分 &gt;= 38</v>
+      </c>
+      <c r="F2" t="str">
+        <v>LP3</v>
+      </c>
+      <c r="G2" t="str">
+        <v>LP3 系统干预</v>
+      </c>
+      <c r="H2" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="I2" t="str">
+        <v>否</v>
+      </c>
+      <c r="J2" t="str">
+        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
+      </c>
+      <c r="K2" t="str">
+        <v>连续两次 LP3 或伴随安全风险</v>
+      </c>
+      <c r="L2" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M2" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N2" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>LP_GRADE_LP2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C3" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="D3" t="str">
+        <v>20</v>
+      </c>
+      <c r="E3" t="str">
+        <v>诊断总分 &gt;= 27</v>
+      </c>
+      <c r="F3" t="str">
+        <v>LP2</v>
+      </c>
+      <c r="G3" t="str">
+        <v>LP2 深入诊断</v>
+      </c>
+      <c r="H3" t="str">
+        <v>high</v>
+      </c>
+      <c r="I3" t="str">
+        <v>否</v>
+      </c>
+      <c r="J3" t="str">
+        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
+      </c>
+      <c r="K3" t="str">
+        <v>连续两次 LP2</v>
+      </c>
+      <c r="L3" t="str">
+        <v>教研组长</v>
+      </c>
+      <c r="M3" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N3" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>LP_GRADE_LP1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>999</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>LP1</v>
+      </c>
+      <c r="G4" t="str">
+        <v>LP1 教师自主支持</v>
+      </c>
+      <c r="H4" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I4" t="str">
+        <v>否</v>
+      </c>
+      <c r="J4" t="str">
+        <v>当前可由教师通过教学策略调整自主支持。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>复评升级到 LP2 或以上</v>
+      </c>
+      <c r="L4" t="str">
+        <v>教研组长</v>
+      </c>
+      <c r="M4" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N4" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
@@ -847,31 +1220,31 @@
         <v>learning_problem</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>维度[LP_RELATION] &gt;= 4.7 且 题[rel3] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>注意力与策略双重薄弱，属学生学习问题模块红线</v>
+        <v>家庭因素对学习的负面影响达到极端水平，可能存在家庭功能问题</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
+        <v>暂停常规学习支持建议，转入学生个体问题模块做适应性评估，并通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>1. 停止当前评估流程 2. 展示危机求助指引 3. 自动创建安全事件 4. 生成转介工单 5. 发送短信通知心理专员</v>
+        <v>停止常规建议输出,提示转入学生个体问题模块,通知心理专员,记录事件</v>
       </c>
       <c r="G2" t="str">
-        <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>
+        <v>完成学生个体问题模块评估且心理专员确认</v>
       </c>
       <c r="H2" t="str">
         <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在学生学习问题评估中触发红线：注意力与策略双重薄弱。请尽快登录系统查看工单。</v>
+        <v>[学生]学习问题评估中家庭关系因素触发红线，请安排个体评估。</v>
       </c>
       <c r="J2" t="str">
-        <v>PRD 8.3</v>
+        <v>学生学习问题手册v1</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/learning_problem/attribution.xlsx
+++ b/business-libraries/test-data/learning_problem/attribution.xlsx
@@ -994,7 +994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1130,51 +1130,139 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_GRADE_LP1</v>
+        <v>LP_GRADE_MOT_LP3</v>
       </c>
       <c r="B4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D4" t="str">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F4" t="str">
-        <v>LP1</v>
+        <v>LP3</v>
       </c>
       <c r="G4" t="str">
-        <v>LP1 教师自主支持</v>
+        <v>LP3 系统干预</v>
       </c>
       <c r="H4" t="str">
-        <v>medium</v>
+        <v>crisis</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
+        <v>动机与学业情绪多项处于高位，建议整合教师、年级和家庭支持。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>连续两次 LP3</v>
+      </c>
+      <c r="L4" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M4" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N4" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>LP_GRADE_MOT_LP2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C5" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="D5" t="str">
+        <v>25</v>
+      </c>
+      <c r="E5" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F5" t="str">
+        <v>LP2</v>
+      </c>
+      <c r="G5" t="str">
+        <v>LP2 深入诊断</v>
+      </c>
+      <c r="H5" t="str">
+        <v>high</v>
+      </c>
+      <c r="I5" t="str">
+        <v>否</v>
+      </c>
+      <c r="J5" t="str">
+        <v>动机或学业情绪存在明显问题，建议结合课堂观察做交叉验证。</v>
+      </c>
+      <c r="K5" t="str">
+        <v>连续两次 LP2</v>
+      </c>
+      <c r="L5" t="str">
+        <v>教研组长</v>
+      </c>
+      <c r="M5" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N5" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LP_GRADE_LP1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>999</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>LP1</v>
+      </c>
+      <c r="G6" t="str">
+        <v>LP1 教师自主支持</v>
+      </c>
+      <c r="H6" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I6" t="str">
+        <v>否</v>
+      </c>
+      <c r="J6" t="str">
         <v>当前可由教师通过教学策略调整自主支持。</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K6" t="str">
         <v>复评升级到 LP2 或以上</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L6" t="str">
         <v>教研组长</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M6" t="str">
         <v>30天后复评</v>
       </c>
-      <c r="N4" t="str">
+      <c r="N6" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/learning_problem/attribution.xlsx
+++ b/business-libraries/test-data/learning_problem/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>三层诊断总分</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>学习行为失序</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="B3" t="str">
         <v>认知加工困难</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="B4" t="str">
         <v>关系层影响</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_AT_MOTIVATION</v>
+        <v>LP_AT_04</v>
       </c>
       <c r="B5" t="str">
         <v>内驱动机不足</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_AT_EFFICACY</v>
+        <v>LP_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>习得性无助</v>
@@ -691,13 +691,13 @@
         <v>LP_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[LP_BEHAVIOR] &gt;= 4</v>
+        <v>维度[LP_S1D1] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
@@ -714,13 +714,13 @@
         <v>LP_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[LP_BEHAVIOR] &gt;= 3</v>
+        <v>维度[LP_S1D1] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,13 +737,13 @@
         <v>LP_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="C4" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>题[beh4] &gt;= 4</v>
+        <v>题[q4] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>2</v>
@@ -760,13 +760,13 @@
         <v>LP_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[LP_COGNITION] &gt;= 4</v>
+        <v>维度[LP_S1D2] &gt;= 4</v>
       </c>
       <c r="E5" t="str">
         <v>3</v>
@@ -783,13 +783,13 @@
         <v>LP_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="C6" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[LP_COGNITION] &gt;= 3</v>
+        <v>维度[LP_S1D2] &gt;= 3</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
@@ -806,13 +806,13 @@
         <v>LP_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="C7" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>题[cog3] &gt;= 4</v>
+        <v>题[q7] &gt;= 4</v>
       </c>
       <c r="E7" t="str">
         <v>2</v>
@@ -829,13 +829,13 @@
         <v>LP_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="C8" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[LP_RELATION] &gt;= 4</v>
+        <v>维度[LP_S1D3] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>3</v>
@@ -852,13 +852,13 @@
         <v>LP_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="C9" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[LP_RELATION] &gt;= 3</v>
+        <v>维度[LP_S1D3] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -872,16 +872,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_EV_21</v>
+        <v>LP_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>LP_AT_MOTIVATION</v>
+        <v>LP_AT_04</v>
       </c>
       <c r="C10" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[LP_INTRINSIC] &gt;= 3.5</v>
+        <v>维度[LP_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E10" t="str">
         <v>2.5</v>
@@ -895,16 +895,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_EV_22</v>
+        <v>LP_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>LP_AT_MOTIVATION</v>
+        <v>LP_AT_04</v>
       </c>
       <c r="C11" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[LP_INTRINSIC] &gt;= 3</v>
+        <v>维度[LP_S2D1] &gt;= 3</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -918,16 +918,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_EV_23</v>
+        <v>LP_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>LP_AT_EFFICACY</v>
+        <v>LP_AT_05</v>
       </c>
       <c r="C12" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[LP_SELF_EFFICACY] &gt;= 3.5</v>
+        <v>维度[LP_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E12" t="str">
         <v>3</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_EV_24</v>
+        <v>LP_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>LP_AT_EFFICACY</v>
+        <v>LP_AT_05</v>
       </c>
       <c r="C13" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[LP_SELF_EFFICACY] &gt;= 3</v>
+        <v>维度[LP_S2D3] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_EV_25</v>
+        <v>LP_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="C14" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[LP_ANXIETY] &gt;= 3.5</v>
+        <v>维度[LP_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2</v>
@@ -994,7 +994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1042,43 +1042,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_GRADE_LP3</v>
+        <v>LP_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>诊断总分 &gt;= 38</v>
+        <v>总分 &gt;= 38</v>
       </c>
       <c r="F2" t="str">
-        <v>LP3</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>LP3 系统干预</v>
+        <v>LP0 危机转介</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
+        <v>学习问题达到危机阈值，需立即转介</v>
       </c>
       <c r="K2" t="str">
-        <v>连续两次 LP3 或伴随安全风险</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v>学生学习问题手册v1</v>
@@ -1086,25 +1086,25 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_GRADE_LP2</v>
+        <v>LP_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>诊断总分 &gt;= 27</v>
+        <v>总分 &gt;= 38</v>
       </c>
       <c r="F3" t="str">
-        <v>LP2</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>LP2 深入诊断</v>
+        <v>LP3 系统干预</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1113,16 +1113,16 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
+        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次 LP2</v>
+        <v>连续两次 LP3 或伴随安全风险</v>
       </c>
       <c r="L3" t="str">
-        <v>教研组长</v>
+        <v>年级组长</v>
       </c>
       <c r="M3" t="str">
-        <v>30天后复评</v>
+        <v>14天后复评</v>
       </c>
       <c r="N3" t="str">
         <v>学生学习问题手册v1</v>
@@ -1130,43 +1130,43 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_GRADE_MOT_LP3</v>
+        <v>LP_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>总分 &gt;= 27</v>
       </c>
       <c r="F4" t="str">
-        <v>LP3</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>LP3 系统干预</v>
+        <v>LP2 深入诊断</v>
       </c>
       <c r="H4" t="str">
-        <v>crisis</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>动机与学业情绪多项处于高位，建议整合教师、年级和家庭支持。</v>
+        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次 LP3</v>
+        <v>连续两次 LP2</v>
       </c>
       <c r="L4" t="str">
-        <v>年级组长</v>
+        <v>教研组长</v>
       </c>
       <c r="M4" t="str">
-        <v>14天后复评</v>
+        <v>30天后复评</v>
       </c>
       <c r="N4" t="str">
         <v>学生学习问题手册v1</v>
@@ -1174,25 +1174,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_GRADE_MOT_LP2</v>
+        <v>LP_GR_AUTO_01</v>
       </c>
       <c r="B5" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C5" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D5" t="str">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>LP2</v>
+        <v>orange</v>
       </c>
       <c r="G5" t="str">
-        <v>LP2 深入诊断</v>
+        <v>LP3 系统干预</v>
       </c>
       <c r="H5" t="str">
         <v>high</v>
@@ -1201,16 +1201,16 @@
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>动机或学业情绪存在明显问题，建议结合课堂观察做交叉验证。</v>
+        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次 LP2</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>教研组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v>学生学习问题手册v1</v>
@@ -1218,25 +1218,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_GRADE_LP1</v>
+        <v>LP_GR_AUTO_02</v>
       </c>
       <c r="B6" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>LP_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>999</v>
+        <v>502</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F6" t="str">
-        <v>LP1</v>
+        <v>yellow</v>
       </c>
       <c r="G6" t="str">
-        <v>LP1 教师自主支持</v>
+        <v>LP2 深入诊断</v>
       </c>
       <c r="H6" t="str">
         <v>medium</v>
@@ -1245,24 +1245,68 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>当前可由教师通过教学策略调整自主支持。</v>
+        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
       </c>
       <c r="K6" t="str">
-        <v>复评升级到 LP2 或以上</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>教研组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LP_GR_DEFAULT</v>
+      </c>
+      <c r="B7" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>999</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>green</v>
+      </c>
+      <c r="G7" t="str">
+        <v>LP1 教师自主支持</v>
+      </c>
+      <c r="H7" t="str">
+        <v>low</v>
+      </c>
+      <c r="I7" t="str">
+        <v>否</v>
+      </c>
+      <c r="J7" t="str">
+        <v>本次评估未发现需要重点干预的信号</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1308,19 +1352,19 @@
         <v>learning_problem</v>
       </c>
       <c r="B2" t="str">
-        <v>维度[LP_RELATION] &gt;= 4.7 且 题[rel3] &gt;= 5</v>
+        <v>总分 &gt;= 38</v>
       </c>
       <c r="C2" t="str">
-        <v>家庭因素对学习的负面影响达到极端水平，可能存在家庭功能问题</v>
+        <v>学习问题达到危机阈值，需立即转介</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>暂停常规学习支持建议，转入学生个体问题模块做适应性评估，并通知心理专员</v>
+        <v>转介心理专员/学习支持中心并同步年级组</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出,提示转入学生个体问题模块,通知心理专员,记录事件</v>
+        <v>停止常规建议输出；提示转入学生个体问题模块；通知心理专员；记录事件</v>
       </c>
       <c r="G2" t="str">
         <v>完成学生个体问题模块评估且心理专员确认</v>
@@ -1329,7 +1373,7 @@
         <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[学生]学习问题评估中家庭关系因素触发红线，请安排个体评估。</v>
+        <v>[教师姓名]老师在学生学习问题评估中触发红线，请尽快登录系统查看处置要求。</v>
       </c>
       <c r="J2" t="str">
         <v>学生学习问题手册v1</v>

--- a/business-libraries/test-data/learning_problem/attribution.xlsx
+++ b/business-libraries/test-data/learning_problem/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>三层诊断总分</v>
       </c>
       <c r="E2" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_AT_01</v>
+        <v>LP_AT_BEHAVIOR</v>
       </c>
       <c r="B2" t="str">
         <v>学习行为失序</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="B3" t="str">
         <v>认知加工困难</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_AT_03</v>
+        <v>LP_AT_RELATION</v>
       </c>
       <c r="B4" t="str">
         <v>关系层影响</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_AT_04</v>
+        <v>LP_AT_MOTIVATION</v>
       </c>
       <c r="B5" t="str">
         <v>内驱动机不足</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_AT_05</v>
+        <v>LP_AT_EFFICACY</v>
       </c>
       <c r="B6" t="str">
         <v>习得性无助</v>
@@ -691,13 +691,13 @@
         <v>LP_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>LP_AT_01</v>
+        <v>LP_AT_BEHAVIOR</v>
       </c>
       <c r="C2" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[LP_S1D1] &gt;= 4</v>
+        <v>维度[LP_BEHAVIOR] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
@@ -714,13 +714,13 @@
         <v>LP_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>LP_AT_01</v>
+        <v>LP_AT_BEHAVIOR</v>
       </c>
       <c r="C3" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[LP_S1D1] &gt;= 3</v>
+        <v>维度[LP_BEHAVIOR] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,13 +737,13 @@
         <v>LP_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>LP_AT_01</v>
+        <v>LP_AT_BEHAVIOR</v>
       </c>
       <c r="C4" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D4" t="str">
-        <v>题[q4] &gt;= 4</v>
+        <v>题[beh4] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>2</v>
@@ -760,13 +760,13 @@
         <v>LP_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="C5" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[LP_S1D2] &gt;= 4</v>
+        <v>维度[LP_COGNITION] &gt;= 4</v>
       </c>
       <c r="E5" t="str">
         <v>3</v>
@@ -783,13 +783,13 @@
         <v>LP_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="C6" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[LP_S1D2] &gt;= 3</v>
+        <v>维度[LP_COGNITION] &gt;= 3</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
@@ -806,13 +806,13 @@
         <v>LP_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_COGNITION</v>
       </c>
       <c r="C7" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D7" t="str">
-        <v>题[q7] &gt;= 4</v>
+        <v>题[cog3] &gt;= 4</v>
       </c>
       <c r="E7" t="str">
         <v>2</v>
@@ -829,13 +829,13 @@
         <v>LP_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>LP_AT_03</v>
+        <v>LP_AT_RELATION</v>
       </c>
       <c r="C8" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[LP_S1D3] &gt;= 4</v>
+        <v>维度[LP_RELATION] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>3</v>
@@ -852,13 +852,13 @@
         <v>LP_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>LP_AT_03</v>
+        <v>LP_AT_RELATION</v>
       </c>
       <c r="C9" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[LP_S1D3] &gt;= 3</v>
+        <v>维度[LP_RELATION] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -872,16 +872,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_EV_09</v>
+        <v>LP_EV_21</v>
       </c>
       <c r="B10" t="str">
-        <v>LP_AT_04</v>
+        <v>LP_AT_MOTIVATION</v>
       </c>
       <c r="C10" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[LP_S2D1] &gt;= 3.5</v>
+        <v>维度[LP_INTRINSIC] &gt;= 3.5</v>
       </c>
       <c r="E10" t="str">
         <v>2.5</v>
@@ -895,16 +895,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_EV_10</v>
+        <v>LP_EV_22</v>
       </c>
       <c r="B11" t="str">
-        <v>LP_AT_04</v>
+        <v>LP_AT_MOTIVATION</v>
       </c>
       <c r="C11" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[LP_S2D1] &gt;= 3</v>
+        <v>维度[LP_INTRINSIC] &gt;= 3</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -918,16 +918,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_EV_11</v>
+        <v>LP_EV_23</v>
       </c>
       <c r="B12" t="str">
-        <v>LP_AT_05</v>
+        <v>LP_AT_EFFICACY</v>
       </c>
       <c r="C12" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[LP_S2D3] &gt;= 3.5</v>
+        <v>维度[LP_SELF_EFFICACY] &gt;= 3.5</v>
       </c>
       <c r="E12" t="str">
         <v>3</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_EV_12</v>
+        <v>LP_EV_24</v>
       </c>
       <c r="B13" t="str">
-        <v>LP_AT_05</v>
+        <v>LP_AT_EFFICACY</v>
       </c>
       <c r="C13" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[LP_S2D3] &gt;= 3</v>
+        <v>维度[LP_SELF_EFFICACY] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_EV_13</v>
+        <v>LP_EV_25</v>
       </c>
       <c r="B14" t="str">
-        <v>LP_AT_03</v>
+        <v>LP_AT_RELATION</v>
       </c>
       <c r="C14" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[LP_S2D2] &gt;= 3.5</v>
+        <v>维度[LP_ANXIETY] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2</v>
@@ -994,7 +994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:P6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1037,74 +1037,86 @@
         <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
+        <v>干预工具</v>
+      </c>
+      <c r="O1" t="str">
+        <v>干预动作</v>
+      </c>
+      <c r="P1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_GR_01</v>
+        <v>LP_GRADE_LP3</v>
       </c>
       <c r="B2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C2" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>总分 &gt;= 38</v>
+        <v>诊断总分 &gt;= 38</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>LP3</v>
       </c>
       <c r="G2" t="str">
-        <v>LP0 危机转介</v>
+        <v>LP3 系统干预</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
       </c>
       <c r="I2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J2" t="str">
-        <v>学习问题达到危机阈值，需立即转介</v>
+        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
       </c>
       <c r="K2" t="str">
+        <v>连续两次 LP3 或伴随安全风险</v>
+      </c>
+      <c r="L2" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M2" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N2" t="str">
         <v/>
       </c>
-      <c r="L2" t="str">
+      <c r="O2" t="str">
         <v/>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_GR_02</v>
+        <v>LP_GRADE_LP2</v>
       </c>
       <c r="B3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C3" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 38</v>
+        <v>诊断总分 &gt;= 27</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>LP2</v>
       </c>
       <c r="G3" t="str">
-        <v>LP3 系统干预</v>
+        <v>LP2 深入诊断</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1113,86 +1125,98 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
+        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次 LP3 或伴随安全风险</v>
+        <v>连续两次 LP2</v>
       </c>
       <c r="L3" t="str">
-        <v>年级组长</v>
+        <v>教研组长</v>
       </c>
       <c r="M3" t="str">
-        <v>14天后复评</v>
+        <v>30天后复评</v>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_GR_03</v>
+        <v>LP_GRADE_MOT_LP3</v>
       </c>
       <c r="B4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v>LP_S1</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D4" t="str">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E4" t="str">
-        <v>总分 &gt;= 27</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>LP3</v>
       </c>
       <c r="G4" t="str">
-        <v>LP2 深入诊断</v>
+        <v>LP3 系统干预</v>
       </c>
       <c r="H4" t="str">
-        <v>medium</v>
+        <v>crisis</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
+        <v>动机与学业情绪多项处于高位，建议整合教师、年级和家庭支持。</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次 LP2</v>
+        <v>连续两次 LP3</v>
       </c>
       <c r="L4" t="str">
-        <v>教研组长</v>
+        <v>年级组长</v>
       </c>
       <c r="M4" t="str">
-        <v>30天后复评</v>
+        <v>14天后复评</v>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_GR_AUTO_01</v>
+        <v>LP_GRADE_MOT_LP2</v>
       </c>
       <c r="B5" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C5" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="D5" t="str">
-        <v>501</v>
+        <v>25</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F5" t="str">
-        <v>orange</v>
+        <v>LP2</v>
       </c>
       <c r="G5" t="str">
-        <v>LP3 系统干预</v>
+        <v>LP2 深入诊断</v>
       </c>
       <c r="H5" t="str">
         <v>high</v>
@@ -1201,42 +1225,48 @@
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
+        <v>动机或学业情绪存在明显问题，建议结合课堂观察做交叉验证。</v>
       </c>
       <c r="K5" t="str">
+        <v>连续两次 LP2</v>
+      </c>
+      <c r="L5" t="str">
+        <v>教研组长</v>
+      </c>
+      <c r="M5" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N5" t="str">
         <v/>
       </c>
-      <c r="L5" t="str">
+      <c r="O5" t="str">
         <v/>
       </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_GR_AUTO_02</v>
+        <v>LP_GRADE_LP1</v>
       </c>
       <c r="B6" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C6" t="str">
-        <v>LP_S2</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>502</v>
+        <v>999</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>yellow</v>
+        <v>LP1</v>
       </c>
       <c r="G6" t="str">
-        <v>LP2 深入诊断</v>
+        <v>LP1 教师自主支持</v>
       </c>
       <c r="H6" t="str">
         <v>medium</v>
@@ -1245,68 +1275,30 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
+        <v>当前可由教师通过教学策略调整自主支持。</v>
       </c>
       <c r="K6" t="str">
+        <v>复评升级到 LP2 或以上</v>
+      </c>
+      <c r="L6" t="str">
+        <v>教研组长</v>
+      </c>
+      <c r="M6" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N6" t="str">
         <v/>
       </c>
-      <c r="L6" t="str">
+      <c r="O6" t="str">
         <v/>
       </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v>学生学习问题手册v1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>LP_GR_DEFAULT</v>
-      </c>
-      <c r="B7" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>999</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>green</v>
-      </c>
-      <c r="G7" t="str">
-        <v>LP1 教师自主支持</v>
-      </c>
-      <c r="H7" t="str">
-        <v>low</v>
-      </c>
-      <c r="I7" t="str">
-        <v>否</v>
-      </c>
-      <c r="J7" t="str">
-        <v>本次评估未发现需要重点干预的信号</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
+      <c r="P6" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1352,19 +1344,19 @@
         <v>learning_problem</v>
       </c>
       <c r="B2" t="str">
-        <v>总分 &gt;= 38</v>
+        <v>维度[LP_RELATION] &gt;= 4.7 且 题[rel3] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>学习问题达到危机阈值，需立即转介</v>
+        <v>家庭因素对学习的负面影响达到极端水平，可能存在家庭功能问题</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>转介心理专员/学习支持中心并同步年级组</v>
+        <v>暂停常规学习支持建议，转入学生个体问题模块做适应性评估，并通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出；提示转入学生个体问题模块；通知心理专员；记录事件</v>
+        <v>停止常规建议输出,提示转入学生个体问题模块,通知心理专员,记录事件</v>
       </c>
       <c r="G2" t="str">
         <v>完成学生个体问题模块评估且心理专员确认</v>
@@ -1373,7 +1365,7 @@
         <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在学生学习问题评估中触发红线，请尽快登录系统查看处置要求。</v>
+        <v>[学生]学习问题评估中家庭关系因素触发红线，请安排个体评估。</v>
       </c>
       <c r="J2" t="str">
         <v>学生学习问题手册v1</v>

--- a/business-libraries/test-data/learning_problem/attribution.xlsx
+++ b/business-libraries/test-data/learning_problem/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>三层诊断总分</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>学习行为失序</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="B3" t="str">
         <v>认知加工困难</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="B4" t="str">
         <v>关系层影响</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_AT_MOTIVATION</v>
+        <v>LP_AT_04</v>
       </c>
       <c r="B5" t="str">
         <v>内驱动机不足</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_AT_EFFICACY</v>
+        <v>LP_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>习得性无助</v>
@@ -691,13 +691,13 @@
         <v>LP_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[LP_BEHAVIOR] &gt;= 4</v>
+        <v>维度[LP_S1D1] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
@@ -714,13 +714,13 @@
         <v>LP_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[LP_BEHAVIOR] &gt;= 3</v>
+        <v>维度[LP_S1D1] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,13 +737,13 @@
         <v>LP_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>LP_AT_BEHAVIOR</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="C4" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>题[beh4] &gt;= 4</v>
+        <v>题[q4] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>2</v>
@@ -760,13 +760,13 @@
         <v>LP_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[LP_COGNITION] &gt;= 4</v>
+        <v>维度[LP_S1D2] &gt;= 4</v>
       </c>
       <c r="E5" t="str">
         <v>3</v>
@@ -783,13 +783,13 @@
         <v>LP_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="C6" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[LP_COGNITION] &gt;= 3</v>
+        <v>维度[LP_S1D2] &gt;= 3</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
@@ -806,13 +806,13 @@
         <v>LP_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>LP_AT_COGNITION</v>
+        <v>LP_AT_02</v>
       </c>
       <c r="C7" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>题[cog3] &gt;= 4</v>
+        <v>题[q7] &gt;= 4</v>
       </c>
       <c r="E7" t="str">
         <v>2</v>
@@ -829,13 +829,13 @@
         <v>LP_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="C8" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[LP_RELATION] &gt;= 4</v>
+        <v>维度[LP_S1D3] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>3</v>
@@ -852,13 +852,13 @@
         <v>LP_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="C9" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[LP_RELATION] &gt;= 3</v>
+        <v>维度[LP_S1D3] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -872,16 +872,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_EV_21</v>
+        <v>LP_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>LP_AT_MOTIVATION</v>
+        <v>LP_AT_04</v>
       </c>
       <c r="C10" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[LP_INTRINSIC] &gt;= 3.5</v>
+        <v>维度[LP_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E10" t="str">
         <v>2.5</v>
@@ -895,16 +895,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_EV_22</v>
+        <v>LP_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>LP_AT_MOTIVATION</v>
+        <v>LP_AT_04</v>
       </c>
       <c r="C11" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[LP_INTRINSIC] &gt;= 3</v>
+        <v>维度[LP_S2D1] &gt;= 3</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -918,16 +918,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_EV_23</v>
+        <v>LP_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>LP_AT_EFFICACY</v>
+        <v>LP_AT_05</v>
       </c>
       <c r="C12" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[LP_SELF_EFFICACY] &gt;= 3.5</v>
+        <v>维度[LP_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E12" t="str">
         <v>3</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_EV_24</v>
+        <v>LP_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>LP_AT_EFFICACY</v>
+        <v>LP_AT_05</v>
       </c>
       <c r="C13" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[LP_SELF_EFFICACY] &gt;= 3</v>
+        <v>维度[LP_S2D3] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_EV_25</v>
+        <v>LP_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>LP_AT_RELATION</v>
+        <v>LP_AT_03</v>
       </c>
       <c r="C14" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[LP_ANXIETY] &gt;= 3.5</v>
+        <v>维度[LP_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2</v>
@@ -994,7 +994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1048,43 +1048,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_GRADE_LP3</v>
+        <v>LP_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>诊断总分 &gt;= 38</v>
+        <v>总分 &gt;= 38</v>
       </c>
       <c r="F2" t="str">
-        <v>LP3</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>LP3 系统干预</v>
+        <v>LP0 危机转介</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
+        <v>学习问题达到危机阈值，需立即转介</v>
       </c>
       <c r="K2" t="str">
-        <v>连续两次 LP3 或伴随安全风险</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -1098,25 +1098,25 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_GRADE_LP2</v>
+        <v>LP_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>诊断总分 &gt;= 27</v>
+        <v>总分 &gt;= 38</v>
       </c>
       <c r="F3" t="str">
-        <v>LP2</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>LP2 深入诊断</v>
+        <v>LP3 系统干预</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1125,16 +1125,16 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
+        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次 LP2</v>
+        <v>连续两次 LP3 或伴随安全风险</v>
       </c>
       <c r="L3" t="str">
-        <v>教研组长</v>
+        <v>年级组长</v>
       </c>
       <c r="M3" t="str">
-        <v>30天后复评</v>
+        <v>14天后复评</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -1148,43 +1148,43 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_GRADE_MOT_LP3</v>
+        <v>LP_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>总分 &gt;= 27</v>
       </c>
       <c r="F4" t="str">
-        <v>LP3</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>LP3 系统干预</v>
+        <v>LP2 深入诊断</v>
       </c>
       <c r="H4" t="str">
-        <v>crisis</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>动机与学业情绪多项处于高位，建议整合教师、年级和家庭支持。</v>
+        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次 LP3</v>
+        <v>连续两次 LP2</v>
       </c>
       <c r="L4" t="str">
-        <v>年级组长</v>
+        <v>教研组长</v>
       </c>
       <c r="M4" t="str">
-        <v>14天后复评</v>
+        <v>30天后复评</v>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -1198,25 +1198,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_GRADE_MOT_LP2</v>
+        <v>LP_GR_AUTO_01</v>
       </c>
       <c r="B5" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C5" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="D5" t="str">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>LP2</v>
+        <v>orange</v>
       </c>
       <c r="G5" t="str">
-        <v>LP2 深入诊断</v>
+        <v>LP3 系统干预</v>
       </c>
       <c r="H5" t="str">
         <v>high</v>
@@ -1225,16 +1225,16 @@
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>动机或学业情绪存在明显问题，建议结合课堂观察做交叉验证。</v>
+        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次 LP2</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>教研组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -1248,25 +1248,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_GRADE_LP1</v>
+        <v>LP_GR_AUTO_02</v>
       </c>
       <c r="B6" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>LP_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>999</v>
+        <v>502</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F6" t="str">
-        <v>LP1</v>
+        <v>yellow</v>
       </c>
       <c r="G6" t="str">
-        <v>LP1 教师自主支持</v>
+        <v>LP2 深入诊断</v>
       </c>
       <c r="H6" t="str">
         <v>medium</v>
@@ -1275,16 +1275,16 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>当前可由教师通过教学策略调整自主支持。</v>
+        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
       </c>
       <c r="K6" t="str">
-        <v>复评升级到 LP2 或以上</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>教研组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -1293,12 +1293,62 @@
         <v/>
       </c>
       <c r="P6" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LP_GR_DEFAULT</v>
+      </c>
+      <c r="B7" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>999</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>green</v>
+      </c>
+      <c r="G7" t="str">
+        <v>LP1 教师自主支持</v>
+      </c>
+      <c r="H7" t="str">
+        <v>low</v>
+      </c>
+      <c r="I7" t="str">
+        <v>否</v>
+      </c>
+      <c r="J7" t="str">
+        <v>本次评估未发现需要重点干预的信号</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <v>学生学习问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1344,19 +1394,19 @@
         <v>learning_problem</v>
       </c>
       <c r="B2" t="str">
-        <v>维度[LP_RELATION] &gt;= 4.7 且 题[rel3] &gt;= 5</v>
+        <v>量表[LP_S1].总分 &gt;= 38</v>
       </c>
       <c r="C2" t="str">
-        <v>家庭因素对学习的负面影响达到极端水平，可能存在家庭功能问题</v>
+        <v>学习问题达到危机阈值，需立即转介</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>暂停常规学习支持建议，转入学生个体问题模块做适应性评估，并通知心理专员</v>
+        <v>转介心理专员/学习支持中心并同步年级组</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出,提示转入学生个体问题模块,通知心理专员,记录事件</v>
+        <v>停止常规建议输出；提示转入学生个体问题模块；通知心理专员；记录事件</v>
       </c>
       <c r="G2" t="str">
         <v>完成学生个体问题模块评估且心理专员确认</v>
@@ -1365,7 +1415,7 @@
         <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[学生]学习问题评估中家庭关系因素触发红线，请安排个体评估。</v>
+        <v>[教师姓名]老师在学生学习问题评估中触发红线，请尽快登录系统查看处置要求。</v>
       </c>
       <c r="J2" t="str">
         <v>学生学习问题手册v1</v>

--- a/business-libraries/test-data/learning_problem/attribution.xlsx
+++ b/business-libraries/test-data/learning_problem/attribution.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,39 +426,16 @@
         <v>依赖维度编码</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>诊断总分</v>
-      </c>
-      <c r="B2" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C2" t="str">
-        <v>总分</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>LP_S1</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -497,31 +474,31 @@
         <v>LP_AT_01</v>
       </c>
       <c r="B2" t="str">
-        <v>学习行为失序</v>
+        <v>注意缺陷/多动冲动倾向</v>
       </c>
       <c r="C2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="D2" t="str">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="E2" t="str">
-        <v>learning_problem,behavior</v>
+        <v>cognition,attention,learning_problem</v>
       </c>
       <c r="F2" t="str">
-        <v>学习行为持续失序，且提醒或奖励等外部推动手段效果有限。</v>
+        <v>SNAP-IV 筛查显示注意缺陷或多动-冲动阳性项≥6项（得分≥2），提示 ADHD 样表现，需专业评估确认。</v>
       </c>
       <c r="G2" t="str">
-        <v>作业拖延、课堂分心；提醒和奖励都不再有效</v>
+        <v>任一组（师/家）≥6项≥2分；走神、坐不住、冲动抢答</v>
       </c>
       <c r="H2" t="str">
-        <v>可能与执行功能、任务难度或环境干扰相关</v>
+        <v>神经发育层面因素，常与执行功能薄弱相关</v>
       </c>
       <c r="I2" t="str">
-        <v>完成一周学习行为观察，记录课堂参与、作业完成和测验表现的模式</v>
+        <v>结合课堂观察交叉核实，与家长沟通后转介专业评估</v>
       </c>
       <c r="J2" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -529,31 +506,31 @@
         <v>LP_AT_02</v>
       </c>
       <c r="B3" t="str">
-        <v>认知加工困难</v>
+        <v>执行功能薄弱</v>
       </c>
       <c r="C3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="D3" t="str">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="str">
-        <v>learning_problem,cognition</v>
+        <v>cognition,executive,learning_problem</v>
       </c>
       <c r="F3" t="str">
-        <v>学生对核心概念的理解停留在表面，缺少可迁移的学习策略。</v>
+        <v>大脑前额叶"总指挥"能力弱：抑制控制、工作记忆、认知灵活不足，表现为拖拉、丢三落四、钻牛角尖。</v>
       </c>
       <c r="G3" t="str">
-        <v>会做原题不会变式；独立解题时容易卡住</v>
+        <v>拖拉、丢三落四、难以切换思路</v>
       </c>
       <c r="H3" t="str">
-        <v>缺少元认知策略或前置知识存在断层</v>
+        <v>执行功能发育未成熟或缺乏针对性训练</v>
       </c>
       <c r="I3" t="str">
-        <v>试用一项教学支架：从示范、提示、提问、同伴互助中选一项并记录效果</v>
+        <v>开展认知训练（注意力/记忆/执行功能）并配合课堂支持</v>
       </c>
       <c r="J3" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +538,7 @@
         <v>LP_AT_03</v>
       </c>
       <c r="B4" t="str">
-        <v>关系层影响</v>
+        <v>学习策略不足</v>
       </c>
       <c r="C4" t="str">
         <v>learning_problem</v>
@@ -570,22 +547,22 @@
         <v>1.2</v>
       </c>
       <c r="E4" t="str">
-        <v>learning_problem,relation</v>
+        <v>strategy,cognition,learning_problem</v>
       </c>
       <c r="F4" t="str">
-        <v>师生关系、同伴比较或家庭期待明显影响了学生的学习投入。</v>
+        <v>认知策略与元认知策略使用水平低（总均分≤2.5），"努力但效率低"，知识会但方法差。</v>
       </c>
       <c r="G4" t="str">
-        <v>换老师后表现差异明显；因同伴比较而回避课堂</v>
+        <v>不会预习复习、笔记差、不会组织信息</v>
       </c>
       <c r="H4" t="str">
-        <v>课堂归属感不足或家庭期待与能力错配</v>
+        <v>策略缺失中段起显，缺方法训练</v>
       </c>
       <c r="I4" t="str">
-        <v>本周创造一次该学生在课堂上被正向看见的机会</v>
+        <v>按策略剖面补对应策略（复述/组织/计划/监控/调节）</v>
       </c>
       <c r="J4" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +570,31 @@
         <v>LP_AT_04</v>
       </c>
       <c r="B5" t="str">
-        <v>内驱动机不足</v>
+        <v>元认知缺失</v>
       </c>
       <c r="C5" t="str">
         <v>learning_problem</v>
       </c>
       <c r="D5" t="str">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="str">
-        <v>learning_problem,motivation</v>
+        <v>strategy,metacognition,learning_problem</v>
       </c>
       <c r="F5" t="str">
-        <v>学习完全依赖外部推动，学生缺少自主的学习目标。</v>
+        <v>"对自己怎么学"的觉察和调控不足：不会计划、不监控理解、不调节方法，学完不知道自己会不会。</v>
       </c>
       <c r="G5" t="str">
-        <v>没人督促就不学；学习是为了避免批评</v>
+        <v>学完不知道自己会不会、一变就不会</v>
       </c>
       <c r="H5" t="str">
-        <v>长期外部控制导致自主感缺失</v>
+        <v>缺少元认知训练，教师带问不足</v>
       </c>
       <c r="I5" t="str">
-        <v>让学生自己选择一项本周的学习任务并定义完成标准</v>
+        <v>用元认知提问清单训练计划-监控-调节</v>
       </c>
       <c r="J5" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
@@ -625,43 +602,587 @@
         <v>LP_AT_05</v>
       </c>
       <c r="B6" t="str">
-        <v>习得性无助</v>
+        <v>工作记忆容量不足</v>
       </c>
       <c r="C6" t="str">
         <v>learning_problem</v>
       </c>
       <c r="D6" t="str">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="E6" t="str">
-        <v>learning_problem,efficacy</v>
+        <v>cognition,learning_problem</v>
       </c>
       <c r="F6" t="str">
-        <v>学生认为再努力也学不好，把失败归因于能力而非方法。</v>
+        <v>大脑"临时桌面"太小，听一句忘一句，边听边记困难。</v>
       </c>
       <c r="G6" t="str">
-        <v>「我就是学不会数学」；放弃尝试</v>
+        <v>听讲跟不上、记不住多步指令</v>
       </c>
       <c r="H6" t="str">
+        <v>工作记忆容量小，信息超载</v>
+      </c>
+      <c r="I6" t="str">
+        <v>任务拆小步、给书面提示、减少记忆负担</v>
+      </c>
+      <c r="J6" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LP_AT_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>学习动机缺失（无动机）</v>
+      </c>
+      <c r="C7" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>motivation,learning_problem</v>
+      </c>
+      <c r="F7" t="str">
+        <v>无动机明显（≥4分）：不清楚学习有什么用、学不学无所谓，最危险的动机状态。</v>
+      </c>
+      <c r="G7" t="str">
+        <v>「学这干嘛」「学不学无所谓」</v>
+      </c>
+      <c r="H7" t="str">
+        <v>长期外部控制、意义感缺失</v>
+      </c>
+      <c r="I7" t="str">
+        <v>先点燃动力（HERO 活动包），再谈方法</v>
+      </c>
+      <c r="J7" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LP_AT_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>外控动机主导</v>
+      </c>
+      <c r="C8" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D8" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>motivation,learning_problem</v>
+      </c>
+      <c r="F8" t="str">
+        <v>为奖励/惩罚而学，外在调节高于内在动机，一旦外部控制消失学习即停。</v>
+      </c>
+      <c r="G8" t="str">
+        <v>没人催就不学、为表扬而学</v>
+      </c>
+      <c r="H8" t="str">
+        <v>长期奖励惩罚驱动形成外控</v>
+      </c>
+      <c r="I8" t="str">
+        <v>逐步把"要我学"变"我要学"，给选择权</v>
+      </c>
+      <c r="J8" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LP_AT_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>学业情绪困扰</v>
+      </c>
+      <c r="C9" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>emotion,learning_problem</v>
+      </c>
+      <c r="F9" t="str">
+        <v>消极学业情绪（焦虑/无聊/羞耻）偏多（消极≥3.0）或积极情绪不足（积极≤2.5），情绪性学习困难。</v>
+      </c>
+      <c r="G9" t="str">
+        <v>一提学习就烦/慌/怕</v>
+      </c>
+      <c r="H9" t="str">
+        <v>长期挫败、评价压力、课堂无趣</v>
+      </c>
+      <c r="I9" t="str">
+        <v>优先疏导情绪（团体辅导/家长指导），再谈策略</v>
+      </c>
+      <c r="J9" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LP_AT_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>考试焦虑</v>
+      </c>
+      <c r="C10" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D10" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>emotion,anxiety,learning_problem</v>
+      </c>
+      <c r="F10" t="str">
+        <v>考试前紧张不安、怕考不好，焦虑情绪影响正常发挥。</v>
+      </c>
+      <c r="G10" t="str">
+        <v>考前紧张、怕考不好、越想越慌</v>
+      </c>
+      <c r="H10" t="str">
+        <v>评价压力、家长期待、负性经验</v>
+      </c>
+      <c r="I10" t="str">
+        <v>焦虑疏导+家长沟通降低评价压力</v>
+      </c>
+      <c r="J10" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LP_AT_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>自我效能感不足</v>
+      </c>
+      <c r="C11" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>motivation,efficacy,learning_problem</v>
+      </c>
+      <c r="F11" t="str">
+        <v>"觉得我不行"：效能感低，成绩差时归因于自己能力不行，出现习得性无助。</v>
+      </c>
+      <c r="G11" t="str">
+        <v>「我就是学不会」、放弃尝试</v>
+      </c>
+      <c r="H11" t="str">
         <v>长期失败经验累积且缺少归因引导</v>
       </c>
-      <c r="I6" t="str">
-        <v>设计一个必然能成功的最小任务，并明确把成功归因到具体方法上</v>
-      </c>
-      <c r="J6" t="str">
-        <v>学生学习问题手册v1</v>
+      <c r="I11" t="str">
+        <v>设计必然成功的最小任务，归因从能力转向方法</v>
+      </c>
+      <c r="J11" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_AT_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>希望感缺失</v>
+      </c>
+      <c r="C12" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>motivation,hope,learning_problem</v>
+      </c>
+      <c r="F12" t="str">
+        <v>"没有盼头"：缺少目标和路径感，学习没有奔头。</v>
+      </c>
+      <c r="G12" t="str">
+        <v>「学不学都差不多」</v>
+      </c>
+      <c r="H12" t="str">
+        <v>目标模糊、看不到努力与结果的联系</v>
+      </c>
+      <c r="I12" t="str">
+        <v>目标阶梯+路径思维训练（HERO 希望感活动）</v>
+      </c>
+      <c r="J12" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_AT_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>韧性不足</v>
+      </c>
+      <c r="C13" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D13" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>motivation,resilience,learning_problem</v>
+      </c>
+      <c r="F13" t="str">
+        <v>"摔了爬不起来"：面对困难容易放弃，抗挫能力弱。</v>
+      </c>
+      <c r="G13" t="str">
+        <v>一遇难题就放弃、受挫后长时间消沉</v>
+      </c>
+      <c r="H13" t="str">
+        <v>缺乏抗挫训练与支持性反馈</v>
+      </c>
+      <c r="I13" t="str">
+        <v>抗挫训练+认知重评，设置"有挑战但可达"的任务</v>
+      </c>
+      <c r="J13" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_AT_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>学业差距与偏科</v>
+      </c>
+      <c r="C14" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D14" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E14" t="str">
+        <v>academic,learning_problem</v>
+      </c>
+      <c r="F14" t="str">
+        <v>某科或某知识点长期薄弱、明显落后于其他（低于均值≥10或连续下滑），含知识断层与偏科模式。</v>
+      </c>
+      <c r="G14" t="str">
+        <v>偏科、低于班级均值、连续下滑</v>
+      </c>
+      <c r="H14" t="str">
+        <v>知识断层滚雪球、三年级断层、策略落差</v>
+      </c>
+      <c r="I14" t="str">
+        <v>学业差距分析定位断层点，分学科补策略</v>
+      </c>
+      <c r="J14" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_AT_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>三年级知识断层</v>
+      </c>
+      <c r="C15" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D15" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>academic,learning_problem</v>
+      </c>
+      <c r="F15" t="str">
+        <v>三年级学业难度骤升导致成绩和心理集中滑坡：不是孩子退步，是认知要求跳级。</v>
+      </c>
+      <c r="G15" t="str">
+        <v>三年级突然下滑、偏科显现</v>
+      </c>
+      <c r="H15" t="str">
+        <v>抽象思维要求提升、前置知识断层</v>
+      </c>
+      <c r="I15" t="str">
+        <v>重点查知识断层与策略缺口，专项补漏</v>
+      </c>
+      <c r="J15" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_AT_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>课堂参与不足</v>
+      </c>
+      <c r="C16" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E16" t="str">
+        <v>behavior,classroom,learning_problem</v>
+      </c>
+      <c r="F16" t="str">
+        <v>课堂任务投入、举手发言、听讲理解不足（课堂观察总均分&lt;3或单维≤2）。</v>
+      </c>
+      <c r="G16" t="str">
+        <v>上课不投入、不举手、跟不上</v>
+      </c>
+      <c r="H16" t="str">
+        <v>任务难度不匹配、归属感不足、注意力问题</v>
+      </c>
+      <c r="I16" t="str">
+        <v>课堂支持策略（任务分层/即时反馈/正向看见）</v>
+      </c>
+      <c r="J16" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_AT_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>依恋不安全倾向</v>
+      </c>
+      <c r="C17" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D17" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E17" t="str">
+        <v>relation,attachment,learning_problem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>亲子依恋安全性不足：风险项反向均分≥3.5，回避/矛盾/紊乱倾向，关系底座不稳学习难稳。</v>
+      </c>
+      <c r="G17" t="str">
+        <v>不愿求助、情绪易炸、师生/亲子冲突多</v>
+      </c>
+      <c r="H17" t="str">
+        <v>养育环境风险、亲子冲突频发</v>
+      </c>
+      <c r="I17" t="str">
+        <v>依恋修复亲子活动+家校沟通，先补关系再补学习</v>
+      </c>
+      <c r="J17" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LP_AT_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>师生关系紧张</v>
+      </c>
+      <c r="C18" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D18" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E18" t="str">
+        <v>relation,learning_problem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>师生关系影响课堂归属与求助意愿，学生怕老师、不敢问。</v>
+      </c>
+      <c r="G18" t="str">
+        <v>怕老师、换老师后表现差异大</v>
+      </c>
+      <c r="H18" t="str">
+        <v>批评式互动、课堂归属感不足</v>
+      </c>
+      <c r="I18" t="str">
+        <v>创造课堂正向被看见的机会，重建师生联结</v>
+      </c>
+      <c r="J18" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LP_AT_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>同伴关系边缘化</v>
+      </c>
+      <c r="C19" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D19" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>relation,peer,learning_problem</v>
+      </c>
+      <c r="F19" t="str">
+        <v>被同伴排斥或边缘化，课堂回避、不敢表达，影响学习投入。</v>
+      </c>
+      <c r="G19" t="str">
+        <v>被孤立、不敢发言、回避集体活动</v>
+      </c>
+      <c r="H19" t="str">
+        <v>同伴排斥、社交技能不足</v>
+      </c>
+      <c r="I19" t="str">
+        <v>同伴支持配对+合作任务设计</v>
+      </c>
+      <c r="J19" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LP_AT_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>家庭养育环境风险</v>
+      </c>
+      <c r="C20" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D20" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E20" t="str">
+        <v>family,learning_problem</v>
+      </c>
+      <c r="F20" t="str">
+        <v>家庭结构、养育方式、屏幕时间、亲子冲突等风险因素参与学习问题（高控制/高压、屏幕过量等）。</v>
+      </c>
+      <c r="G20" t="str">
+        <v>高控制高压、屏幕过量、亲子冲突频发</v>
+      </c>
+      <c r="H20" t="str">
+        <v>养育方式不当、家庭冲突、陪伴缺失</v>
+      </c>
+      <c r="I20" t="str">
+        <v>家庭生态画像+家长指导，先建家校关系</v>
+      </c>
+      <c r="J20" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LP_AT_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>班级系统生态问题</v>
+      </c>
+      <c r="C21" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D21" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E21" t="str">
+        <v>system,class,learning_problem</v>
+      </c>
+      <c r="F21" t="str">
+        <v>问题涉及班级整体：学风、群体焦虑、纪律、关系生态（班级生态图五维风险）。</v>
+      </c>
+      <c r="G21" t="str">
+        <v>班级整体纪律差、群体焦虑、关系生态失衡</v>
+      </c>
+      <c r="H21" t="str">
+        <v>班级规则与关系系统未建立</v>
+      </c>
+      <c r="I21" t="str">
+        <v>学校干预方案（课堂支持/同伴支持/心育工程）</v>
+      </c>
+      <c r="J21" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>LP_AT_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>项目小组协作障碍</v>
+      </c>
+      <c r="C22" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D22" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>system,project,learning_problem</v>
+      </c>
+      <c r="F22" t="str">
+        <v>项目化小组角色缺位、任务分工不清、协作摩擦（个体vs系统因素未区分）。</v>
+      </c>
+      <c r="G22" t="str">
+        <v>小组推诿、掉队、协作摩擦</v>
+      </c>
+      <c r="H22" t="str">
+        <v>角色匹配不当、分工不清、动力不足</v>
+      </c>
+      <c r="I22" t="str">
+        <v>差异化设计+角色匹配，降低协作摩擦</v>
+      </c>
+      <c r="J22" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LP_AT_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>元系统思维薄弱</v>
+      </c>
+      <c r="C23" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="D23" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E23" t="str">
+        <v>cognition,thinking,learning_problem</v>
+      </c>
+      <c r="F23" t="str">
+        <v>六力特色思维层问题：信息归类混乱/逻辑链条断裂/反思调控缺失，"一听就懂、一做就错"。</v>
+      </c>
+      <c r="G23" t="str">
+        <v>逻辑乱、不会拆解问题、反思缺失</v>
+      </c>
+      <c r="H23" t="str">
+        <v>思维教学不足、缺少结构化训练</v>
+      </c>
+      <c r="I23" t="str">
+        <v>元系统思维训练课程（归类-链条-反思）</v>
+      </c>
+      <c r="J23" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -697,16 +1218,16 @@
         <v>LP_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[LP_S1D1] &gt;= 4</v>
+        <v>维度[LP_S1D1] &gt;= 2</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
       </c>
       <c r="F2" t="str">
-        <v>行为层得分处于高位，学习行为持续失序</v>
+        <v>教师/家长任一注意缺陷阳性项≥6项（≥2分）提示注意缺陷倾向</v>
       </c>
       <c r="G2" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -720,16 +1241,16 @@
         <v>LP_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[LP_S1D1] &gt;= 3</v>
+        <v>维度[LP_S1D2] &gt;= 2</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>行为层出现需要关注的信号</v>
+        <v>教师/家长任一动-冲动阳性项≥6项（≥2分）提示多动-冲动倾向</v>
       </c>
       <c r="G3" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -743,16 +1264,16 @@
         <v>LP_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>题[q4] &gt;= 4</v>
+        <v>维度[LP_S1D1] &gt;= 1.5</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="str">
-        <v>提醒和奖励等外部推动手段已经失效</v>
+        <v>注意缺陷维度出现需要关注的信号</v>
       </c>
       <c r="G4" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
@@ -760,22 +1281,22 @@
         <v>LP_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_AT_02</v>
+        <v>LP_AT_01</v>
       </c>
       <c r="C5" t="str">
         <v>LP_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[LP_S1D2] &gt;= 4</v>
+        <v>维度[LP_S1D2] &gt;= 1.5</v>
       </c>
       <c r="E5" t="str">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="str">
-        <v>认知层得分处于高位，理解停留在表面</v>
+        <v>多动-冲动维度出现需要关注的信号</v>
       </c>
       <c r="G5" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
@@ -789,16 +1310,16 @@
         <v>LP_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[LP_S1D2] &gt;= 3</v>
+        <v>维度[LP_S1D2] &gt;= 2</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F6" t="str">
-        <v>认知层出现需要关注的信号</v>
+        <v>多动冲动明显常提示抑制控制等执行功能弱</v>
       </c>
       <c r="G6" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="7">
@@ -812,16 +1333,16 @@
         <v>LP_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>题[q7] &gt;= 4</v>
+        <v>维度[LP_S1D1] &gt;= 2</v>
       </c>
       <c r="E7" t="str">
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>缺少元认知策略，独立解题时容易卡住</v>
+        <v>注意缺陷明显常提示工作记忆/注意控制弱</v>
       </c>
       <c r="G7" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="8">
@@ -832,19 +1353,19 @@
         <v>LP_AT_03</v>
       </c>
       <c r="C8" t="str">
-        <v>LP_S1</v>
+        <v>LP_S2</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[LP_S1D3] &gt;= 4</v>
+        <v>总分 &gt;= 3.5</v>
       </c>
       <c r="E8" t="str">
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>关系层得分处于高位，关系因素明显影响学习</v>
+        <v>策略总均分≤2.5，策略使用薄弱（反向计分后≥3.5）</v>
       </c>
       <c r="G8" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="9">
@@ -855,19 +1376,19 @@
         <v>LP_AT_03</v>
       </c>
       <c r="C9" t="str">
-        <v>LP_S1</v>
+        <v>LP_S2</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[LP_S1D3] &gt;= 3</v>
+        <v>总分 &gt;= 2.5</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="str">
-        <v>关系层出现需要关注的信号</v>
+        <v>策略总均分处于中等偏下（反向计分后≥2.5）</v>
       </c>
       <c r="G9" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="10">
@@ -881,16 +1402,16 @@
         <v>LP_S2</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[LP_S2D1] &gt;= 3.5</v>
+        <v>维度[LP_S2D3] &gt;= 3.5 或 维度[LP_S2D4] &gt;= 3.5 且 维度[LP_S2D5] &gt;= 3.5</v>
       </c>
       <c r="E10" t="str">
         <v>2.5</v>
       </c>
       <c r="F10" t="str">
-        <v>内在动机维度偏低，学习依赖外部推动</v>
+        <v>元认知策略（计划/监控/调节）薄弱</v>
       </c>
       <c r="G10" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="11">
@@ -904,16 +1425,16 @@
         <v>LP_S2</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[LP_S2D1] &gt;= 3</v>
+        <v>维度[LP_S2D3] &gt;= 2.5 或 维度[LP_S2D4] &gt;= 2.5 且 维度[LP_S2D5] &gt;= 2.5</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>内在动机出现下降信号</v>
+        <v>元认知策略出现需要关注的信号</v>
       </c>
       <c r="G11" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="12">
@@ -927,16 +1448,16 @@
         <v>LP_S2</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[LP_S2D3] &gt;= 3.5</v>
+        <v>维度[LP_S2D4] &gt;= 3.5</v>
       </c>
       <c r="E12" t="str">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F12" t="str">
-        <v>学业自我效能偏低，出现习得性无助信号</v>
+        <v>边学边查能力弱，常与工作记忆容量不足相关</v>
       </c>
       <c r="G12" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="13">
@@ -944,22 +1465,22 @@
         <v>LP_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>LP_AT_05</v>
+        <v>LP_AT_06</v>
       </c>
       <c r="C13" t="str">
-        <v>LP_S2</v>
+        <v>LP_S3</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[LP_S2D3] &gt;= 3</v>
+        <v>维度[LP_S3D4] &gt;= 4</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>学业自我效能需要关注</v>
+        <v>无动机≥4，动机风险（按文档判读标准）</v>
       </c>
       <c r="G13" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="14">
@@ -967,34 +1488,586 @@
         <v>LP_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>LP_AT_03</v>
+        <v>LP_AT_06</v>
       </c>
       <c r="C14" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="D14" t="str">
+        <v>维度[LP_S3D4] &gt;= 3</v>
+      </c>
+      <c r="E14" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F14" t="str">
+        <v>无动机维度出现需要关注的信号</v>
+      </c>
+      <c r="G14" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_EV_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>LP_AT_07</v>
+      </c>
+      <c r="C15" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="D15" t="str">
+        <v>维度[LP_S3D3] &gt;= 4</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F15" t="str">
+        <v>外在调节≥4，外控动机明显（文档：外在&gt;内在→动机风险）</v>
+      </c>
+      <c r="G15" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_EV_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>LP_AT_07</v>
+      </c>
+      <c r="C16" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="D16" t="str">
+        <v>维度[LP_S3D3] &gt;= 3</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>外控动机出现需要关注的信号</v>
+      </c>
+      <c r="G16" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_EV_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>LP_AT_08</v>
+      </c>
+      <c r="C17" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="D17" t="str">
+        <v>维度[LP_S4D2] &gt;= 3</v>
+      </c>
+      <c r="E17" t="str">
+        <v>3</v>
+      </c>
+      <c r="F17" t="str">
+        <v>消极情绪≥3.0，情绪性学习困难（按文档判读标准）</v>
+      </c>
+      <c r="G17" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LP_EV_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>LP_AT_08</v>
+      </c>
+      <c r="C18" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="D18" t="str">
+        <v>维度[LP_S4D1] &gt;= 3.5</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>积极情绪≤2.5（反向计分后≥3.5），积极情绪不足</v>
+      </c>
+      <c r="G18" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LP_EV_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>LP_AT_09</v>
+      </c>
+      <c r="C19" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="D19" t="str">
+        <v>维度[LP_S4D2] &gt;= 3.5</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str">
+        <v>消极情绪偏高，含焦虑成分明显</v>
+      </c>
+      <c r="G19" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LP_EV_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>LP_AT_09</v>
+      </c>
+      <c r="C20" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="D20" t="str">
+        <v>题[q7] &gt;= 4</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F20" t="str">
+        <v>「考试前我会紧张不安」频繁出现（反向计分后≥4）</v>
+      </c>
+      <c r="G20" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LP_EV_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>LP_AT_10</v>
+      </c>
+      <c r="C21" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="D21" t="str">
+        <v>维度[LP_S4D1] &gt;= 3.5</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F21" t="str">
+        <v>积极情绪不足，含「我相信自己能学好」等效能信号偏低</v>
+      </c>
+      <c r="G21" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>LP_EV_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>LP_AT_10</v>
+      </c>
+      <c r="C22" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="D22" t="str">
+        <v>题[q3] &gt;= 4</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F22" t="str">
+        <v>「我相信自己能学好」明显偏低（反向计分后≥4）</v>
+      </c>
+      <c r="G22" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LP_EV_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>LP_AT_11</v>
+      </c>
+      <c r="C23" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="D23" t="str">
+        <v>维度[LP_S3D1] &gt;= 4</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>内在动机不足（反向计分后≥4），学习缺乏兴趣与奔头</v>
+      </c>
+      <c r="G23" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>LP_EV_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>LP_AT_12</v>
+      </c>
+      <c r="C24" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D24" t="str">
+        <v>题[q8] &gt;= 4</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2</v>
+      </c>
+      <c r="F24" t="str">
+        <v>「面对困难的坚持」差（反向计分后≥4），抗挫弱</v>
+      </c>
+      <c r="G24" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>LP_EV_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>LP_AT_13</v>
+      </c>
+      <c r="C25" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="D25" t="str">
+        <v>总分 &gt;= 1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>3</v>
+      </c>
+      <c r="F25" t="str">
+        <v>任一学科低于均值或连续下滑，薄弱预警</v>
+      </c>
+      <c r="G25" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>LP_EV_25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>LP_AT_13</v>
+      </c>
+      <c r="C26" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="D26" t="str">
+        <v>维度[LP_S7D1] &gt;= 0.6</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>3科及以上薄弱/偏科，需系统归因</v>
+      </c>
+      <c r="G26" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>LP_EV_26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>LP_AT_14</v>
+      </c>
+      <c r="C27" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="D27" t="str">
+        <v>维度[LP_S7D1] &gt;= 0.6</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2</v>
+      </c>
+      <c r="F27" t="str">
+        <v>多科薄弱常对应知识断层（含三年级现象）</v>
+      </c>
+      <c r="G27" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>LP_EV_27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>LP_AT_14</v>
+      </c>
+      <c r="C28" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="D28" t="str">
+        <v>总分 &gt;= 1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F28" t="str">
+        <v>存在薄弱或下滑信号，优先排查断层</v>
+      </c>
+      <c r="G28" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>LP_EV_28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>LP_AT_15</v>
+      </c>
+      <c r="C29" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D29" t="str">
+        <v>维度[LP_S6D1] &gt;= 3.5</v>
+      </c>
+      <c r="E29" t="str">
+        <v>3</v>
+      </c>
+      <c r="F29" t="str">
+        <v>课堂参与≤2.5（反向计分后≥3.5），投入与发言不足</v>
+      </c>
+      <c r="G29" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>LP_EV_29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>LP_AT_15</v>
+      </c>
+      <c r="C30" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D30" t="str">
+        <v>总分 &gt;= 3</v>
+      </c>
+      <c r="E30" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F30" t="str">
+        <v>总均分&lt;3（反向计分后≥3），整体需关注</v>
+      </c>
+      <c r="G30" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>LP_EV_30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>LP_AT_16</v>
+      </c>
+      <c r="C31" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="D31" t="str">
+        <v>维度[LP_S5D4] &gt;= 3.5</v>
+      </c>
+      <c r="E31" t="str">
+        <v>3</v>
+      </c>
+      <c r="F31" t="str">
+        <v>风险项反向均分≥3.5，回避/矛盾/紊乱倾向</v>
+      </c>
+      <c r="G31" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>LP_EV_31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>LP_AT_16</v>
+      </c>
+      <c r="C32" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="D32" t="str">
+        <v>维度[LP_S5D4] &gt;= 3</v>
+      </c>
+      <c r="E32" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F32" t="str">
+        <v>依恋风险项出现需要关注的信号</v>
+      </c>
+      <c r="G32" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>LP_EV_32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>LP_AT_17</v>
+      </c>
+      <c r="C33" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D33" t="str">
+        <v>维度[LP_S6D3] &gt;= 3.5</v>
+      </c>
+      <c r="E33" t="str">
+        <v>2</v>
+      </c>
+      <c r="F33" t="str">
+        <v>社会情绪维度弱（反向计分后≥3.5），师生互动与情绪稳定差</v>
+      </c>
+      <c r="G33" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>LP_EV_33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>LP_AT_18</v>
+      </c>
+      <c r="C34" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D34" t="str">
+        <v>维度[LP_S6D3] &gt;= 3</v>
+      </c>
+      <c r="E34" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F34" t="str">
+        <v>社会情绪维度出现需要关注的信号，同伴合作弱</v>
+      </c>
+      <c r="G34" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>LP_EV_34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>LP_AT_19</v>
+      </c>
+      <c r="C35" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="D35" t="str">
+        <v>维度[LP_S5D4] &gt;= 3</v>
+      </c>
+      <c r="E35" t="str">
+        <v>2</v>
+      </c>
+      <c r="F35" t="str">
+        <v>依恋风险项偏高，提示家庭养育环境存在风险因素</v>
+      </c>
+      <c r="G35" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>LP_EV_35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>LP_AT_20</v>
+      </c>
+      <c r="C36" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D36" t="str">
+        <v>维度[LP_S6D3] &gt;= 4</v>
+      </c>
+      <c r="E36" t="str">
+        <v>2</v>
+      </c>
+      <c r="F36" t="str">
+        <v>社会情绪单维≤2（反向计分后≥4），需重点干预</v>
+      </c>
+      <c r="G36" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>LP_EV_36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>LP_AT_21</v>
+      </c>
+      <c r="C37" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D37" t="str">
+        <v>维度[LP_S6D1] &gt;= 3.5</v>
+      </c>
+      <c r="E37" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F37" t="str">
+        <v>课堂参与弱可能外溢到小组协作（近似信号）</v>
+      </c>
+      <c r="G37" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>LP_EV_37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>LP_AT_22</v>
+      </c>
+      <c r="C38" t="str">
         <v>LP_S2</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D38" t="str">
         <v>维度[LP_S2D2] &gt;= 3.5</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E38" t="str">
         <v>2</v>
       </c>
-      <c r="F14" t="str">
-        <v>学业焦虑明显，可能与课堂关系或家庭期待相关</v>
-      </c>
-      <c r="G14" t="str">
-        <v>学生学习问题手册v1</v>
+      <c r="F38" t="str">
+        <v>组织策略弱（反向计分后≥3.5），提纲/思维导图等结构化思维不足</v>
+      </c>
+      <c r="G38" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1060,13 +2133,13 @@
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>总分 &gt;= 38</v>
+        <v>维度[LP_S1D1] &gt;= 2 且 维度[LP_S1D2] &gt;= 2</v>
       </c>
       <c r="F2" t="str">
         <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>LP0 危机转介</v>
+        <v>高风险-建议转介评估</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
@@ -1075,25 +2148,25 @@
         <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>学习问题达到危机阈值，需立即转介</v>
+        <v>ADHD 样表现提示，需专业评估确认，不宜直接下结论</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>连续两次筛查阳性或伴随明显行为安全风险</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>心理教师/专业评估机构（家长知情同意后）</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>4-8周后复评追踪变化</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>LP_RX_15</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>转介专业评估；开展认知功能剖面分析；同步家长沟通</v>
       </c>
       <c r="P2" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -1104,19 +2177,19 @@
         <v>learning_problem</v>
       </c>
       <c r="C3" t="str">
-        <v>LP_S1</v>
+        <v>LP_S4</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 38</v>
+        <v>维度[LP_S4D2] &gt;= 3 且 维度[LP_S4D1] &gt;= 3.5</v>
       </c>
       <c r="F3" t="str">
         <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>LP3 系统干预</v>
+        <v>中高-情绪与关系干预</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1125,25 +2198,25 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
+        <v>情绪性学习困难信号，需情绪疏导优先</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次 LP3 或伴随安全风险</v>
+        <v>情绪困扰持续2周以上或伴随行为退缩</v>
       </c>
       <c r="L3" t="str">
-        <v>年级组长</v>
+        <v>心理教师</v>
       </c>
       <c r="M3" t="str">
-        <v>14天后复评</v>
+        <v>30天后复评</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>LP_RX_43</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>转介心理教师评估情绪状态；开展团体辅导或家长指导</v>
       </c>
       <c r="P3" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +2227,19 @@
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v>LP_S1</v>
+        <v>LP_S2</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>总分 &gt;= 27</v>
+        <v>总分 &gt;= 3.5</v>
       </c>
       <c r="F4" t="str">
         <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>LP2 深入诊断</v>
+        <v>中-策略与学业支持</v>
       </c>
       <c r="H4" t="str">
         <v>medium</v>
@@ -1175,10 +2248,10 @@
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
+        <v>策略缺失定位，需专项策略辅导</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次 LP2</v>
+        <v>干预4周无改善或伴随成绩持续下滑</v>
       </c>
       <c r="L4" t="str">
         <v>教研组长</v>
@@ -1187,95 +2260,95 @@
         <v>30天后复评</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>LP_RX_29</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>开展学科策略辅导；结合错题管理与预习复习训练</v>
       </c>
       <c r="P4" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_GR_AUTO_01</v>
+        <v>LP_GR_04</v>
       </c>
       <c r="B5" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C5" t="str">
-        <v>LP_S2</v>
+        <v>LP_S7</v>
       </c>
       <c r="D5" t="str">
-        <v>501</v>
+        <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>总分 &gt;= 1</v>
       </c>
       <c r="F5" t="str">
-        <v>orange</v>
+        <v>blue</v>
       </c>
       <c r="G5" t="str">
-        <v>LP3 系统干预</v>
+        <v>中低-学业薄弱预警</v>
       </c>
       <c r="H5" t="str">
-        <v>high</v>
+        <v>low</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>多个层面同时受阻，建议整合教师、年级和家庭支持，制定系统干预计划。</v>
+        <v>学业薄弱/偏科预警，需归因定位</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>多科同时下滑（≥3科）或持续两个阶段无改善</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>期中/期末复评</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>LP_RX_16</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>开展学业差距分析；排查家庭与情绪因素</v>
       </c>
       <c r="P5" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_GR_AUTO_02</v>
+        <v>LP_GR_AUTO_01</v>
       </c>
       <c r="B6" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C6" t="str">
-        <v>LP_S2</v>
+        <v>LP_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F6" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="G6" t="str">
-        <v>LP2 深入诊断</v>
+        <v>中高-情绪与关系干预</v>
       </c>
       <c r="H6" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>需要进一步诊断，建议结合课堂观察做交叉验证后再匹配工具。</v>
+        <v>情绪性学习困难信号，需情绪疏导优先</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -1293,62 +2366,612 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_GR_DEFAULT</v>
+        <v>LP_GR_AUTO_02</v>
       </c>
       <c r="B7" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>LP_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>999</v>
+        <v>502</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F7" t="str">
-        <v>green</v>
+        <v>yellow</v>
       </c>
       <c r="G7" t="str">
-        <v>LP1 教师自主支持</v>
+        <v>中-策略与学业支持</v>
       </c>
       <c r="H7" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
       </c>
       <c r="J7" t="str">
+        <v>策略缺失定位，需专项策略辅导</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LP_GR_AUTO_03</v>
+      </c>
+      <c r="B8" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C8" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>503</v>
+      </c>
+      <c r="E8" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F8" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G8" t="str">
+        <v>中低-学业薄弱预警</v>
+      </c>
+      <c r="H8" t="str">
+        <v>low</v>
+      </c>
+      <c r="I8" t="str">
+        <v>否</v>
+      </c>
+      <c r="J8" t="str">
+        <v>学业薄弱/偏科预警，需归因定位</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LP_GR_AUTO_04</v>
+      </c>
+      <c r="B9" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C9" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="D9" t="str">
+        <v>504</v>
+      </c>
+      <c r="E9" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F9" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G9" t="str">
+        <v>中高-情绪与关系干预</v>
+      </c>
+      <c r="H9" t="str">
+        <v>high</v>
+      </c>
+      <c r="I9" t="str">
+        <v>否</v>
+      </c>
+      <c r="J9" t="str">
+        <v>情绪性学习困难信号，需情绪疏导优先</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LP_GR_AUTO_05</v>
+      </c>
+      <c r="B10" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C10" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="D10" t="str">
+        <v>505</v>
+      </c>
+      <c r="E10" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G10" t="str">
+        <v>中-策略与学业支持</v>
+      </c>
+      <c r="H10" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I10" t="str">
+        <v>否</v>
+      </c>
+      <c r="J10" t="str">
+        <v>策略缺失定位，需专项策略辅导</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LP_GR_AUTO_06</v>
+      </c>
+      <c r="B11" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C11" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="D11" t="str">
+        <v>506</v>
+      </c>
+      <c r="E11" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F11" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G11" t="str">
+        <v>中低-学业薄弱预警</v>
+      </c>
+      <c r="H11" t="str">
+        <v>low</v>
+      </c>
+      <c r="I11" t="str">
+        <v>否</v>
+      </c>
+      <c r="J11" t="str">
+        <v>学业薄弱/偏科预警，需归因定位</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_GR_AUTO_07</v>
+      </c>
+      <c r="B12" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C12" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="D12" t="str">
+        <v>507</v>
+      </c>
+      <c r="E12" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G12" t="str">
+        <v>中高-情绪与关系干预</v>
+      </c>
+      <c r="H12" t="str">
+        <v>high</v>
+      </c>
+      <c r="I12" t="str">
+        <v>否</v>
+      </c>
+      <c r="J12" t="str">
+        <v>情绪性学习困难信号，需情绪疏导优先</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_GR_AUTO_08</v>
+      </c>
+      <c r="B13" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C13" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="D13" t="str">
+        <v>508</v>
+      </c>
+      <c r="E13" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G13" t="str">
+        <v>中-策略与学业支持</v>
+      </c>
+      <c r="H13" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I13" t="str">
+        <v>否</v>
+      </c>
+      <c r="J13" t="str">
+        <v>策略缺失定位，需专项策略辅导</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_GR_AUTO_09</v>
+      </c>
+      <c r="B14" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C14" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="D14" t="str">
+        <v>509</v>
+      </c>
+      <c r="E14" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F14" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G14" t="str">
+        <v>中低-学业薄弱预警</v>
+      </c>
+      <c r="H14" t="str">
+        <v>low</v>
+      </c>
+      <c r="I14" t="str">
+        <v>否</v>
+      </c>
+      <c r="J14" t="str">
+        <v>学业薄弱/偏科预警，需归因定位</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_GR_AUTO_10</v>
+      </c>
+      <c r="B15" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C15" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>510</v>
+      </c>
+      <c r="E15" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F15" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G15" t="str">
+        <v>中高-情绪与关系干预</v>
+      </c>
+      <c r="H15" t="str">
+        <v>high</v>
+      </c>
+      <c r="I15" t="str">
+        <v>否</v>
+      </c>
+      <c r="J15" t="str">
+        <v>情绪性学习困难信号，需情绪疏导优先</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_GR_AUTO_11</v>
+      </c>
+      <c r="B16" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C16" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>511</v>
+      </c>
+      <c r="E16" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F16" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G16" t="str">
+        <v>中-策略与学业支持</v>
+      </c>
+      <c r="H16" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I16" t="str">
+        <v>否</v>
+      </c>
+      <c r="J16" t="str">
+        <v>策略缺失定位，需专项策略辅导</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_GR_AUTO_12</v>
+      </c>
+      <c r="B17" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C17" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="D17" t="str">
+        <v>512</v>
+      </c>
+      <c r="E17" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F17" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G17" t="str">
+        <v>中低-学业薄弱预警</v>
+      </c>
+      <c r="H17" t="str">
+        <v>low</v>
+      </c>
+      <c r="I17" t="str">
+        <v>否</v>
+      </c>
+      <c r="J17" t="str">
+        <v>学业薄弱/偏科预警，需归因定位</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LP_GR_DEFAULT</v>
+      </c>
+      <c r="B18" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>999</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>green</v>
+      </c>
+      <c r="G18" t="str">
+        <v>暂无明显信号</v>
+      </c>
+      <c r="H18" t="str">
+        <v>low</v>
+      </c>
+      <c r="I18" t="str">
+        <v>否</v>
+      </c>
+      <c r="J18" t="str">
         <v>本次评估未发现需要重点干预的信号</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>学生学习问题手册v1</v>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1394,31 +3017,31 @@
         <v>learning_problem</v>
       </c>
       <c r="B2" t="str">
-        <v>量表[LP_S1].总分 &gt;= 38</v>
+        <v>量表[LP_S1].维度[LP_S1D1] &gt;= 2 且 量表[LP_S1].维度[LP_S1D2] &gt;= 2</v>
       </c>
       <c r="C2" t="str">
-        <v>学习问题达到危机阈值，需立即转介</v>
+        <v>ADHD 样表现提示，需专业评估确认，不宜直接下结论</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>转介心理专员/学习支持中心并同步年级组</v>
+        <v>停止常规建议输出；转介心理教师或专业机构评估（家长知情同意后）；同步年级组</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出；提示转入学生个体问题模块；通知心理专员；记录事件</v>
+        <v>停止常规建议输出；通知心理专员；记录事件</v>
       </c>
       <c r="G2" t="str">
-        <v>完成学生个体问题模块评估且心理专员确认</v>
+        <v>专业评估确认风险解除后</v>
       </c>
       <c r="H2" t="str">
         <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在学生学习问题评估中触发红线，请尽快登录系统查看处置要求。</v>
+        <v>[教师姓名]老师的学习问题评估触发高风险红线（SNAP-IV 阳性提示），请尽快登录系统查看转介处置要求。</v>
       </c>
       <c r="J2" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
